--- a/docs/table/报价系统功能基础数据功能结构所需字段（3.0版）(含规则).xlsx
+++ b/docs/table/报价系统功能基础数据功能结构所需字段（3.0版）(含规则).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\temp\表结构\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\docs\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C0841-CACB-4CCA-8DE4-7E2F06659239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F0B96B-5CB2-4CE5-A656-83B0EC92C8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" firstSheet="4" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素单价" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="314">
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1351,6 +1351,397 @@
     </r>
   </si>
   <si>
+    <t>供应商编号</t>
+  </si>
+  <si>
+    <t>产能表</t>
+  </si>
+  <si>
+    <t>工序编号</t>
+  </si>
+  <si>
+    <t>默认不良率 (%)</t>
+  </si>
+  <si>
+    <t>电镀方案编号</t>
+  </si>
+  <si>
+    <t>电镀方案版本</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电镀元素（如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ag / Au / Ni / Sn / Cu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来源网站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单价抓取规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电镀面积 (cm²)（局部镀时填，整体镀=surface_area）</t>
+  </si>
+  <si>
+    <t>镀层厚度 (μm)</t>
+  </si>
+  <si>
+    <t>电镀要求 / 规格描述</t>
+  </si>
+  <si>
+    <t>价格版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>费用类型:电镀加工费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>费用类型:电镀材料费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当电镀方案编号不为空时不导入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不良率%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>料号表</t>
+  </si>
+  <si>
+    <t>料号（业务唯一）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单重 (g/pcs)</t>
+  </si>
+  <si>
+    <t>料号</t>
+  </si>
+  <si>
+    <t>年降顺序</t>
+  </si>
+  <si>
+    <t>年降系数 (%)</t>
+  </si>
+  <si>
+    <t>单次年降值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货币</t>
+  </si>
+  <si>
+    <t>计价单位</t>
+  </si>
+  <si>
+    <t>降价次数</t>
+  </si>
+  <si>
+    <t>年降系数表</t>
+  </si>
+  <si>
+    <t>付款方式</t>
+  </si>
+  <si>
+    <t>基础货币</t>
+  </si>
+  <si>
+    <t>报价货币</t>
+  </si>
+  <si>
+    <t>QUOTE / PRICING=QUOTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>费用类型:元素价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取用规则</t>
+  </si>
+  <si>
+    <t>升水价 / 手续费</t>
+  </si>
+  <si>
+    <t>物料BOM主表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料BOM子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>料号表</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUOTE / PRICING / BOTH = QUOTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MATERIAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（物料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>BOM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / ASSEMBLY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（组成件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>BOM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = MATERIAL</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户编号由导入时系统提供</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bom_type=ELEMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">/* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> */ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为2000,当主键料号为同一个,但是组件料号组成不一样 包括元素不一样和用量不一样则需要新增版本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>规则为版本+1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素BOM子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素BOM主表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配特性最新的版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格类型:材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格了卫星:材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元素代码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>材料料号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>零件号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>耗材料号</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bom_type=ASSEMBLY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格类型:组成件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电镀方案表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">/* </t>
     </r>
@@ -1371,396 +1762,14 @@
       </rPr>
       <t xml:space="preserve"> */</t>
     </r>
-  </si>
-  <si>
-    <t>供应商编号</t>
-  </si>
-  <si>
-    <t>产能表</t>
-  </si>
-  <si>
-    <t>工序编号</t>
-  </si>
-  <si>
-    <t>默认不良率 (%)</t>
-  </si>
-  <si>
-    <t>电镀方案编号</t>
-  </si>
-  <si>
-    <t>电镀方案版本</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电镀元素（如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ag / Au / Ni / Sn / Cu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来源网站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单价抓取规则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电镀面积 (cm²)（局部镀时填，整体镀=surface_area）</t>
-  </si>
-  <si>
-    <t>镀层厚度 (μm)</t>
-  </si>
-  <si>
-    <t>电镀要求 / 规格描述</t>
-  </si>
-  <si>
-    <t>价格版本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>费用类型:电镀加工费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>费用类型:电镀材料费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当电镀方案编号不为空时不导入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不良率%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>料号表</t>
-  </si>
-  <si>
-    <t>料号（业务唯一）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单重 (g/pcs)</t>
-  </si>
-  <si>
-    <t>料号</t>
-  </si>
-  <si>
-    <t>年降顺序</t>
-  </si>
-  <si>
-    <t>年降系数 (%)</t>
-  </si>
-  <si>
-    <t>单次年降值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>货币</t>
-  </si>
-  <si>
-    <t>计价单位</t>
-  </si>
-  <si>
-    <t>降价次数</t>
-  </si>
-  <si>
-    <t>年降系数表</t>
-  </si>
-  <si>
-    <t>付款方式</t>
-  </si>
-  <si>
-    <t>基础货币</t>
-  </si>
-  <si>
-    <t>报价货币</t>
-  </si>
-  <si>
-    <t>QUOTE / PRICING=QUOTE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>费用类型:元素价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>取用规则</t>
-  </si>
-  <si>
-    <t>升水价 / 手续费</t>
-  </si>
-  <si>
-    <t>物料BOM主表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料BOM子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-      </rPr>
-      <t>料号表</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QUOTE / PRICING / BOTH = QUOTE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MATERIAL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（物料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>BOM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / ASSEMBLY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（组成件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>BOM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> = MATERIAL</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>客户编号由导入时系统提供</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bom_type=ELEMENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">/* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>特性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> */ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为2000,当主键料号为同一个,但是组件料号组成不一样 包括元素不一样和用量不一样则需要新增版本</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>规则为版本+1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素BOM子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素BOM主表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配特性最新的版本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格类型:材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格了卫星:材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>元素代码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>材料料号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>零件号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>耗材料号</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bom_type=ASSEMBLY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格类型:组成件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电镀方案表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净重</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2485,10 +2494,10 @@
         <v>223</v>
       </c>
       <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
         <v>291</v>
-      </c>
-      <c r="C6" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -2505,10 +2514,10 @@
         <v>227</v>
       </c>
       <c r="G7" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>293</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>294</v>
       </c>
       <c r="I7" s="20" t="s">
         <v>245</v>
@@ -2712,7 +2721,7 @@
         <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="66" x14ac:dyDescent="0.2">
@@ -2864,12 +2873,12 @@
         <v>222</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A9" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
@@ -3078,7 +3087,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -3086,12 +3095,12 @@
         <v>229</v>
       </c>
       <c r="C10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
@@ -3105,7 +3114,7 @@
         <v>258</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>230</v>
@@ -3506,7 +3515,7 @@
         <v>222</v>
       </c>
       <c r="B13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -3520,7 +3529,7 @@
         <v>225</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>253</v>
@@ -3635,7 +3644,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
@@ -3643,7 +3652,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>251</v>
@@ -3655,7 +3664,7 @@
         <v>246</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -3806,7 +3815,7 @@
         <v>252</v>
       </c>
       <c r="C10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
@@ -3961,36 +3970,36 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.75" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>264</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>265</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="G7" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="H7" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="I7" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="J7" s="20" t="s">
         <v>270</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -4079,16 +4088,16 @@
         <v>223</v>
       </c>
       <c r="B6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" t="s">
         <v>273</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>274</v>
       </c>
-      <c r="E6" t="s">
-        <v>275</v>
-      </c>
       <c r="H6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
@@ -4099,7 +4108,7 @@
         <v>193</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>251</v>
@@ -4114,7 +4123,7 @@
         <v>246</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -4155,15 +4164,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="33" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>278</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -4253,30 +4262,30 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="C9" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="F9" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="G9" s="20" t="s">
         <v>285</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4369,13 +4378,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="G5" s="20" t="s">
         <v>289</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>290</v>
       </c>
       <c r="H5" s="20" t="s">
         <v>228</v>
@@ -4498,16 +4507,16 @@
     </row>
     <row r="6" spans="1:10" ht="104.25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="G6" t="s">
         <v>299</v>
-      </c>
-      <c r="G6" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -4517,13 +4526,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="49.5" x14ac:dyDescent="0.2">
@@ -4536,11 +4545,11 @@
       <c r="E9" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>232</v>
+      <c r="F9" s="21" t="s">
+        <v>312</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>233</v>
+        <v>313</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>234</v>
@@ -4551,7 +4560,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="49.5" x14ac:dyDescent="0.2">
@@ -4736,13 +4745,13 @@
     </row>
     <row r="8" spans="1:11" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C8" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>301</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
@@ -4760,10 +4769,10 @@
     </row>
     <row r="12" spans="1:11" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
@@ -4875,10 +4884,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="37.5" x14ac:dyDescent="0.2">
@@ -5043,7 +5052,7 @@
         <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.2">
@@ -5253,7 +5262,7 @@
         <v>222</v>
       </c>
       <c r="C9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="33" x14ac:dyDescent="0.2">
@@ -5433,7 +5442,7 @@
         <v>252</v>
       </c>
       <c r="C7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -5527,7 +5536,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -5543,7 +5552,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
